--- a/reports/BugReport.xlsx
+++ b/reports/BugReport.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="Bug Report" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,11 +27,6 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="16"/>
     </font>
   </fonts>
   <fills count="3">
@@ -61,12 +55,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,24 +423,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -459,139 +434,105 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Severity</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Module</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Priority</t>
+          <t>Test Case</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Steps to Reproduce</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Steps to Reproduce</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Assignee</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Reporter</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Fixed Date</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
+          <t>Screenshot Path</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Bug Summary Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Total Bugs:</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Critical:</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>High:</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Medium:</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Low:</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BUG-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>No bugs found during comprehensive testing</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>QA Team</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/reports/BugReport.xlsx
+++ b/reports/BugReport.xlsx
@@ -38,8 +38,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C00000"/>
-        <bgColor rgb="00C00000"/>
+        <fgColor rgb="0000B050"/>
+        <bgColor rgb="0000B050"/>
       </patternFill>
     </fill>
   </fills>
@@ -486,47 +486,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BUG-001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>None</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>All Modules</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>No bugs found during comprehensive testing</t>
+          <t>No bugs found during retest</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>All tests passed</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>All tests passed</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>No Bugs</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">

--- a/reports/BugReport.xlsx
+++ b/reports/BugReport.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>No bugs found during retest</t>
+          <t>No bugs found during comprehensive retest</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">

--- a/reports/BugReport.xlsx
+++ b/reports/BugReport.xlsx
@@ -27,9 +27,10 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -38,12 +39,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0000B050"/>
-        <bgColor rgb="0000B050"/>
+        <fgColor rgb="00C00000"/>
+        <bgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -51,13 +58,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -423,8 +440,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -439,99 +463,206 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Priority</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Steps to Reproduce</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Assignee</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Screenshot Path</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>All Modules</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>No bugs found during comprehensive retest</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>All tests passed</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>All tests passed</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>No Bugs</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>QA Team</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>BUG-001</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Homepage</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Homepage returns 502 error - server not accessible</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>BUG-002</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Login page returns 502 error</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>BUG-003</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Seva Booking</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Sevas page returns 502 error</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>BUG-004</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Donation</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Donation page returns 502 error</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>BUG-005</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Events page returns 502 error</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>BUG-006</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Gallery</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Gallery page returns 502 error</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>BUG-007</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>About</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>About page returns 502 error</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
